--- a/Result/profitability/6205.xlsx
+++ b/Result/profitability/6205.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.475</v>
+        <v>0.49625</v>
       </c>
       <c r="N2" t="n">
-        <v>38.18</v>
+        <v>37.4275</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.68</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48375</v>
+        <v>0.52625</v>
       </c>
       <c r="N3" t="n">
-        <v>35.92875</v>
+        <v>35.51875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="N4" t="n">
-        <v>34.17</v>
+        <v>33.34375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.47875</v>
+        <v>0.5537500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>31.73125</v>
+        <v>31.3925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5375000000000001</v>
+        <v>0.55625</v>
       </c>
       <c r="N6" t="n">
-        <v>30.22125</v>
+        <v>29.88625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5337500000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>28.8075</v>
+        <v>28.37375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5287500000000001</v>
+        <v>0.57875</v>
       </c>
       <c r="N8" t="n">
-        <v>27.56875</v>
+        <v>27.15375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>373</v>
+      </c>
+      <c r="D75" t="n">
+        <v>239</v>
+      </c>
+      <c r="E75" t="n">
+        <v>134</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>63</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.52625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.51125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.052631578947369</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08443540183112919</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.710000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07000774993541725</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
